--- a/docs/ausruestung_stats.xlsx
+++ b/docs/ausruestung_stats.xlsx
@@ -14,10 +14,10 @@
     <sheet name="Gadgets" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Huelle'!$A$4:$I$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Waffen'!$A$4:$G$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Kerne'!$A$4:$F$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Gadgets'!$A$4:$F$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Huelle'!$A$4:$M$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Waffen'!$A$4:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Kerne'!$A$4:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Gadgets'!$A$4:$F$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -117,13 +117,13 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -132,7 +132,7 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -502,12 +502,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="74" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Schlankes Balancing-Modell fuer den Reframe (GAME_DESIGN §9/§12). Zahlen sind Vorschlaege -- zum Anpassen gedacht.</t>
+          <t>Balancing-Sicht auf das Klassenmodell (GAME_DESIGN §9/§12).</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>Werte</t>
+          <t>Werte (Zahlen)</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -551,15 +551,15 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Huelle / Chassis</t>
+          <t>Huelle</t>
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>ja -- genau eine Signatur-Passive je Huelle</t>
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -570,9 +570,9 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -585,11 +585,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>nein</t>
+        <v>4</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>ja</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
       <c r="B9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
@@ -652,247 +652,315 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Panzerung</t>
+          <t>Energieschild</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>def</t>
+          <t>shield (§11, neu)</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Flache Schadensreduktion (heutiges DEF).</t>
+          <t>Regenerierende Leiste vor der HP. Schwach gegen Energieschaden.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>Tempo</t>
+          <t>Panzerung</t>
         </is>
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>spd</t>
+          <t>def</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Zugtakt -- wie oft die Huelle drankommt.</t>
+          <t>Flache Schadensreduktion (heutiges DEF).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Schaden</t>
+          <t>Tempo</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>power</t>
+          <t>spd</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>Grundschaden des Angriffs.</t>
+          <t>Zugtakt -- wie oft die Huelle drankommt.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
         <is>
-          <t>Reichweite</t>
+          <t>Move</t>
         </is>
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>range_tiles</t>
+          <t>mov</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>Reichweite des Angriffs in Feldern.</t>
+          <t>Bewegungsreichweite je Zug in Feldern.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Energie</t>
+          <t>Traglast</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>en_max</t>
+          <t>weight_capacity</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>Groesse des Energietanks (Mana).</t>
+          <t>Was das Chassis an Ausruestung traegt.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Regeneration</t>
+          <t>Slots</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
+          <t>equip_*-Anker</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Zahl der Ausruestungsslots der Huelle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Schaden</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>power</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Grundschaden des Angriffs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Reichweite</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>range_tiles</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Reichweite des Angriffs in Feldern.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Energie</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>en_max</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Groesse des Energietanks (Mana).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Energie-Regeneration</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
           <t>en_regen</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Energie-Nachschub je Zug.</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Schildregeneration</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>(neu)</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Wie schnell sich das Energieschild wieder auffuellt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Schildbonus</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>(neu, Anteil)</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Anteiliger Aufschlag auf das Schild (0.05 = 5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Hinweise</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>Ausruestungs-Statistik-Liste -- schlankes Balancing-Modell fuer den Reframe</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>(GAME_DESIGN.md §9 / §12). Eine Zeile je Teil, wenige Werte je Zeile.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="7" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Dies ist NICHT die Engine-Tabelle. Die Kampfwerte, die das Spiel wirklich</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>liest, stehen in tools/build_sample_parts.py (STATS). Diese Datei ist die</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>kuratierte BALANCING-Sicht auf das neue Klassenmodell: die Huelle als ein</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Teil, wenige aussagekraeftige Werte je Kategorie -- zum Anfassen und Tunen.</t>
+          <t>Ausruestungs-Statistik-Liste -- Balancing-Sicht auf das Klassenmodell</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr"/>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>(GAME_DESIGN.md §9 / §12). Eine Zeile je Teil.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Umfang der Werte je Kategorie (so gewuenscht):</t>
-        </is>
-      </c>
+      <c r="A30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Huelle  3 Stats + genau eine Signatur-Passive</t>
+          <t>Dies ist NICHT die Engine-Tabelle. Die Kampfwerte, die das Spiel wirklich</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Waffe   2 Stats</t>
+          <t>liest, stehen in tools/build_sample_parts.py (STATS). Diese Datei ist die</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Kern    2 Stats</t>
+          <t>kuratierte BALANCING-Sicht zum Anfassen und Tunen.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Gadget  1 Stat (je Teil ein anderer -- das ist Absicht)</t>
-        </is>
-      </c>
+      <c r="A34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr"/>
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Stand nach dem Balancing-Durchgang: das Modell ist gegenueber dem ersten</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Passive Faehigkeiten sind bewusst NUR an der Huelle -- alle anderen</t>
+          <t>Entwurf (Huelle 3 / Waffe 2 / Kern 2 / Gadget 1) gewachsen. Die Kategorien</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Kategorien tragen keine. (Aktive Faehigkeiten kommen weiter vom Kern, §13,</t>
+          <t>fuehren jetzt:</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>und sind hier absichtlich kein 'Stat'.)</t>
+          <t xml:space="preserve">  Huelle  Integritaet, Energieschild, Panzerung, Tempo, Move, Traglast,</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="inlineStr"/>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">          Slots -- plus genau eine Signatur-Passive je Klasse.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Arbeitsweise: Werte hier (oder in der Excel-Mappe) aendern, dann</t>
+          <t xml:space="preserve">  Waffe   Schaden, Reichweite -- plus Beschreibung (aoe, Angriffsdesign, Last).</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  python3 tools/build_balance_sheet.py</t>
+          <t xml:space="preserve">  Kern    Energie, Energie-Regeneration, Schildregeneration, Schildbonus --</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>erzeugt docs/ausruestung_stats.xlsx neu. Zahlen sind VORSCHLAEGE, abgeleitet</t>
+          <t xml:space="preserve">          plus eine Passive und einen Stat-Bonus je Kern.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>aus dem heutigen Bestand -- als sinnvoller Startpunkt, nicht als Setzung.</t>
+          <t xml:space="preserve">  Gadget  ein Wirk-Wert plus Wirkungstext.</t>
         </is>
       </c>
     </row>
@@ -902,60 +970,133 @@
     <row r="45">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>OFFENE FRAGE (Huelle): der Rahmen fuehrt heute Tempo (SPD, Zugtakt) UND MOV</t>
+          <t>MOV-Frage geklaert: die Huelle fuehrt Tempo (SPD, Zugtakt) UND Move</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>(Bewegungsreichweite je Zug) getrennt. Fuer '3 Stats' habe ich Tempo=SPD</t>
+          <t>(Bewegungsreichweite je Zug) getrennt.</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>gewaehlt und MOV vorerst weggelassen. Sag Bescheid, ob MOV als vierter Wert</t>
-        </is>
-      </c>
+      <c r="A47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>rein soll oder Panzerung/Tempo ersetzt -- dann ziehe ich es nach.</t>
+          <t>Energieschild/Schild kommt aus der Schadensordnung §11 (Panzerung vs. Schild).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>Schildbonus ist ein Anteil (0.05 = 5%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Der Koedersender (EQP-008) ist auf Wunsch vorerst gestrichen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>Schema: je Kategorie eine Liste 'spalten' (key, label, kind, width) und eine</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>Liste 'zeilen'. kind='stat' sind die getunten Zahlen (in der Mappe</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>hervorgehoben), 'desc' beschreibender Text, 'id'/'text' der Rest. Neue Spalte</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7">
+        <f> ein Eintrag in 'spalten' plus das Feld in jeder Zeile.</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>Arbeitsweise: Werte hier (oder in der Excel-Mappe) aendern, dann</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  python3 tools/build_balance_sheet.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="inlineStr">
+        <is>
+          <t>erzeugt docs/ausruestung_stats.xlsx neu.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="27">
-    <mergeCell ref="A25:C25"/>
+  <mergeCells count="33">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A55:C55"/>
+    <mergeCell ref="A50:C50"/>
+    <mergeCell ref="A57:C57"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A33:C33"/>
     <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A53:C53"/>
     <mergeCell ref="A35:C35"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A38:C38"/>
+    <mergeCell ref="A52:C52"/>
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A58:C58"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A30:C30"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A59:C59"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A60:C60"/>
     <mergeCell ref="A36:C36"/>
+    <mergeCell ref="A49:C49"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A54:C54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -967,24 +1108,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="52" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="52" customWidth="1" min="12" max="12"/>
+    <col width="38" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Huelle / Chassis -- 3 Werte + Signatur-Passive</t>
+          <t>Huelle / Chassis -- Werte + Signatur-Passive</t>
         </is>
       </c>
     </row>
@@ -1018,31 +1163,51 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>Energieschild</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
           <t>Panzerung</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Tempo</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Traglast</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>Slots</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Passive -- Wirkung</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Notizen</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>CHS-001</t>
@@ -1059,147 +1224,191 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E5" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Adrenalin</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>Nach einem Kill hat der Vireo für den Zyklus +3 Tempo.</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="44" customHeight="1">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>CHS-002</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>Molok Chassis</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Juggernaut -- Tank, 'ist da und geht nicht'</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>Bollwerk</t>
+        </is>
+      </c>
+      <c r="L6" s="10" t="inlineStr">
+        <is>
+          <t>Schaden, den verbündete DROMEs auf direkt angrenzenden Feldern (orthogonal oder diagonal) nehmen würden, fängt der Molok zu 50% ab.</t>
+        </is>
+      </c>
+      <c r="M6" s="10" t="inlineStr">
+        <is>
+          <t>Langsam ja, geviertelt nein (§9g).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>CHS-003</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Nimbus Chassis</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Technomant -- Magie/Energie-Caster</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Energy-Junky</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>Für jede 10 ausgegebene Energie (für Fähigkeiten) erhöht sich der Schaden des nächsten Angriffs um 10%.</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8" ht="31" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>CHS-004</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Strix Chassis</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Marksman -- Fernkampf, physisch, wenig Leben</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>Nachbrenner</t>
-        </is>
-      </c>
-      <c r="H5" s="5" t="inlineStr">
-        <is>
-          <t>Nach einem Angriff bewegt sich die Vireo bis zu 2 Felder, ohne Zug zu kosten (Hit-and-Run/Rueckzug).</t>
-        </is>
-      </c>
-      <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Startwerte = heutige Summe aus Body+Antrieb+Kopf (Tempo aus SPD).</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="46" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>CHS-002</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
-        <is>
-          <t>Molok Chassis</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>Juggernaut -- Tank, 'ist da und geht nicht'</t>
-        </is>
-      </c>
-      <c r="D6" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="E6" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F6" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Bollwerk</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Hat sich der Molok in diesem Zug nicht bewegt, +3 Panzerung bis zu seinem naechsten Zug.</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Langsam ja, geviertelt nein (§9g) -- Tempo bewusst nicht unter das Vireo-Viertel.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="46" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>CHS-003</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Nimbus Chassis</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Technomant -- Magie/Energie-Caster</t>
-        </is>
-      </c>
-      <c r="D7" s="9" t="n">
-        <v>85</v>
-      </c>
-      <c r="E7" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>Manafluss</t>
-        </is>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Setzt der Nimbus in einem Zug keine Faehigkeit ein, regeneriert er im naechsten Zug +5 Energie zusaetzlich.</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr"/>
-    </row>
-    <row r="8" ht="46" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>CHS-004</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Strix Chassis</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Marksman -- Fernkampf, physisch, wenig Leben</t>
-        </is>
-      </c>
-      <c r="D8" s="9" t="n">
-        <v>70</v>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Fadenkreuz</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Hat sich der Strix in diesem Zug nicht bewegt, +25% Schaden auf seinen Angriff (der stehende Schuetze trifft haerter).</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr"/>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>Straight Line</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>Schießt Strix auf ein Ziel, das orthogonal in einer Linie zu ihm steht, macht er +50% Schaden.</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I8"/>
+  <autoFilter ref="A4:M8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1210,7 +1419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1219,20 +1428,23 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Waffen -- 2 Werte</t>
+          <t>Waffen -- Schaden + Reichweite</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Schaden und Reichweite -- die zwei Zahlen, die eine Waffe im Tactics ausmachen (§3d).</t>
+          <t>Die zwei Kernwerte, dazu Bauart, aoe, Angriffsdesign und Last.</t>
         </is>
       </c>
     </row>
@@ -1269,6 +1481,21 @@
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
+          <t>aoe</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Angriffsdesign</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Last</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
           <t>Notizen</t>
         </is>
       </c>
@@ -1295,14 +1522,27 @@
         </is>
       </c>
       <c r="E5" s="9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
+        <v>3</v>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>kleiner runder Laserpuls</t>
+        </is>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>EQP-003</t>
@@ -1315,7 +1555,7 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Schwer, Flaeche (AoE 1)</t>
+          <t>Schwer, Flaeche</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
@@ -1331,11 +1571,24 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
+          <t>ja (8 angrenzende Felder)</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>großer mörserartiger Schuss</t>
+        </is>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
           <t>Rein mechanisch -- zieht keinen Strom, bezahlt in Gewicht/Tempo.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="18" customHeight="1">
+    <row r="7" ht="31" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>EQP-005</t>
@@ -1357,18 +1610,31 @@
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
+          <t>ja (4 angrenzende Felder orthogonal)</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>kleine Clusterbombe aus Energie</t>
+        </is>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
           <t>Reichweite 1 = Nahkampf, keine Sichtlinie noetig.</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
+    <row r="8" ht="31" customHeight="1">
       <c r="A8" s="10" t="inlineStr">
         <is>
           <t>EQP-007</t>
@@ -1390,19 +1656,32 @@
         </is>
       </c>
       <c r="E8" s="9" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F8" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
+          <t>nein</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>railgunartiger Laserpuls (dreieckig, nach hinten schmaler)</t>
+        </is>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
           <t>Weiteste Reichweite, dafuer leise (niedrige Aggro).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G8"/>
+  <autoFilter ref="A4:J8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1413,28 +1692,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Kerne -- 2 Werte</t>
+          <t>Kerne -- Energie/Schild + Passive</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Energie (Tank) und Regeneration. Die aktive Faehigkeit haengt auch am Kern (§13), ist aber kein Stat.</t>
+          <t>Energie und Regeneration, dazu Schildwerte, eine Passive und ein Stat-Bonus. Die aktive Faehigkeit haengt auch am Kern (§13).</t>
         </is>
       </c>
     </row>
@@ -1461,16 +1745,41 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Regeneration</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
+          <t>Energie-Regen.</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>Schildregen.</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Schildbonus</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Passive -- Wirkung</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Bonus</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Notizen</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
+    <row r="5" ht="44" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>COR-001</t>
@@ -1490,15 +1799,36 @@
         <v>40</v>
       </c>
       <c r="E5" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>Hit &amp; Run</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Trifft Vireo im Zug zweimal (egal ob mit Fähigkeit oder Angriff), darf er sich 2 Felder kostenlos bewegen.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>5 Speed</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Kleinster Tank -- die natuerliche Obergrenze fuer teure Faehigkeiten.</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>COR-002</t>
@@ -1518,11 +1848,32 @@
         <v>70</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="F6" s="10" t="inlineStr"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+        <v>10</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Overchargerepair</t>
+        </is>
+      </c>
+      <c r="I6" s="10" t="inlineStr">
+        <is>
+          <t>Geht das Schild durch zu viel Schaden aus, erhält Molok 2 Züge lang 10% Lebensregeneration.</t>
+        </is>
+      </c>
+      <c r="J6" s="10" t="inlineStr">
+        <is>
+          <t>20 Integrität</t>
+        </is>
+      </c>
+      <c r="K6" s="10" t="inlineStr"/>
+    </row>
+    <row r="7" ht="44" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>COR-003</t>
@@ -1539,12 +1890,33 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Fast Forward</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Setzt Nimbus einen Zug lang keine Fähigkeit ein, hat er danach 50% mehr Energieregeneration, bis er wieder eine Fähigkeit einsetzt.</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>10 Energiepower</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Groesster Tank + hoechste Regeneration -- der Caster-Kern.</t>
         </is>
@@ -1570,68 +1942,131 @@
         <v>50</v>
       </c>
       <c r="E8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Open-Scope</t>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>20% Chance, eine Schwachstelle zu treffen.</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>10 Power</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9" ht="31" customHeight="1">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>COR-005</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Effizienz-Kern</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Loot (Vorschlag §12a)</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F9" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="F8" s="10" t="inlineStr"/>
-    </row>
-    <row r="9" ht="46" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>COR-005</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Effizienz-Kern</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="G9" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Clean-Code</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>20% weniger Energiekosten.</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>20% Cooldownreduktion</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>Signatur: guenstigere Faehigkeiten (-en_cost).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>COR-006</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>Verstaerker-Kern</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Loot (Vorschlag §12a)</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
-        <v>55</v>
-      </c>
-      <c r="E9" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Signatur: guenstigere Faehigkeiten (-en_cost). Der Effekt selbst ist kein Stat -- hier nur Tank/Regeneration.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t>COR-006</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
-        <is>
-          <t>Verstaerker-Kern</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>Loot (Vorschlag §12a)</t>
-        </is>
-      </c>
       <c r="D10" s="9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E10" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>Signatur: teurere, aber groessere Faehigkeiten (mehr Flaeche/Reichweite).</t>
+        <v>5</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Empowering</t>
+        </is>
+      </c>
+      <c r="I10" s="10" t="inlineStr">
+        <is>
+          <t>40% mehr Energiekosten, aber 20% mehr Schaden auf Fähigkeiten.</t>
+        </is>
+      </c>
+      <c r="J10" s="10" t="inlineStr">
+        <is>
+          <t>10 Energiepower</t>
+        </is>
+      </c>
+      <c r="K10" s="10" t="inlineStr">
+        <is>
+          <t>Signatur: teurere, aber groessere Faehigkeiten.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F10"/>
+  <autoFilter ref="A4:K10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1642,28 +2077,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="56" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gadgets -- 1 Wert</t>
+          <t>Gadgets -- ein Wirk-Wert</t>
         </is>
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Support und Schild. Je Teil GENAU EIN Wert -- aber je Teil ein anderer (Schild, Heilung, Sog, Aggro).</t>
+          <t>Support und Schild. Je Teil ein Wert (je Teil ein anderer) plus Wirkungstext. Koedersender vorerst gestrichen.</t>
         </is>
       </c>
     </row>
@@ -1695,11 +2130,11 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Notizen</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
+          <t>Wirkung</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
         <is>
           <t>EQP-002</t>
@@ -1729,7 +2164,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="18" customHeight="1">
+    <row r="6" ht="31" customHeight="1">
       <c r="A6" s="10" t="inlineStr">
         <is>
           <t>EQP-004</t>
@@ -1747,19 +2182,19 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Heilung</t>
+          <t>Integrität</t>
         </is>
       </c>
       <c r="E6" s="9" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F6" s="10" t="inlineStr">
         <is>
-          <t>Heilung je Einsatz (Flaeche um das Ziel).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
+          <t>Lebensregeneration 5% pro Zug (triggert mit dem Beginn des eigenen Zuges).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="31" customHeight="1">
       <c r="A7" s="5" t="inlineStr">
         <is>
           <t>EQP-006</t>
@@ -1777,11 +2212,11 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Sog</t>
+          <t>Energiepower</t>
         </is>
       </c>
       <c r="E7" s="9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1789,38 +2224,8 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>EQP-008</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
-        <is>
-          <t>Koedersender</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>Support</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Aggro</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="n">
-        <v>25</v>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>Einziges Teil mit Aggro-Wert -- provoziert zusaetzlich (Stoersignal).</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:F8"/>
+  <autoFilter ref="A4:F7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/ausruestung_stats.xlsx
+++ b/docs/ausruestung_stats.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Huelle'!$A$4:$M$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Waffen'!$A$4:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Kerne'!$A$4:$K$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Gadgets'!$A$4:$F$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Gadgets'!$A$4:$F$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -502,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C60"/>
+  <dimension ref="A1:C61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1004,66 +1004,73 @@
     <row r="51">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Der Koedersender (EQP-008) ist auf Wunsch vorerst gestrichen.</t>
+          <t>Der Koedersender (EQP-008) behaelt seine normale Aggro (+25) -- nur der</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="7" t="inlineStr"/>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Taunt/die Provokation (Stoersignal) ist gestrichen.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>Schema: je Kategorie eine Liste 'spalten' (key, label, kind, width) und eine</t>
-        </is>
-      </c>
+      <c r="A53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Liste 'zeilen'. kind='stat' sind die getunten Zahlen (in der Mappe</t>
+          <t>Schema: je Kategorie eine Liste 'spalten' (key, label, kind, width) und eine</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
+          <t>Liste 'zeilen'. kind='stat' sind die getunten Zahlen (in der Mappe</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
           <t>hervorgehoben), 'desc' beschreibender Text, 'id'/'text' der Rest. Neue Spalte</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="7">
+    <row r="57">
+      <c r="A57" s="7">
         <f> ein Eintrag in 'spalten' plus das Feld in jeder Zeile.</f>
         <v/>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr"/>
-    </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Arbeitsweise: Werte hier (oder in der Excel-Mappe) aendern, dann</t>
-        </is>
-      </c>
+      <c r="A58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  python3 tools/build_balance_sheet.py</t>
+          <t>Arbeitsweise: Werte hier (oder in der Excel-Mappe) aendern, dann</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">  python3 tools/build_balance_sheet.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
           <t>erzeugt docs/ausruestung_stats.xlsx neu.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="34">
     <mergeCell ref="A41:C41"/>
     <mergeCell ref="A37:C37"/>
     <mergeCell ref="A46:C46"/>
@@ -1096,6 +1103,7 @@
     <mergeCell ref="A36:C36"/>
     <mergeCell ref="A49:C49"/>
     <mergeCell ref="A45:C45"/>
+    <mergeCell ref="A61:C61"/>
     <mergeCell ref="A54:C54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2077,7 +2085,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2098,7 +2106,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Support und Schild. Je Teil ein Wert (je Teil ein anderer) plus Wirkungstext. Koedersender vorerst gestrichen.</t>
+          <t>Support und Schild. Je Teil ein Wert (je Teil ein anderer) plus Wirkungstext. Koedersender: Aggro bleibt, Taunt gestrichen.</t>
         </is>
       </c>
     </row>
@@ -2224,8 +2232,38 @@
         </is>
       </c>
     </row>
+    <row r="8" ht="44" customHeight="1">
+      <c r="A8" s="10" t="inlineStr">
+        <is>
+          <t>EQP-008</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>Koedersender</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Support</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Aggro</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
+        <is>
+          <t>Erzeugt zusätzliche Aggro (+25) -- zieht Aufmerksamkeit auf sich. Ohne Taunt/Provokation (Stoersignal gestrichen).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F7"/>
+  <autoFilter ref="A4:F8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>